--- a/ibmi_reservations.xlsx
+++ b/ibmi_reservations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\temp\bob-for-ibmi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2724267-7661-4CC4-B1CF-5F0BF4FFB5CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7597BCF-8541-47DB-9BCA-A423F007ED2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{EC50F79E-0434-4875-B5AE-7696D6B4F07C}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{916D8ED8-43CB-4AB7-AF7E-14CA3C1C2411}"/>
   </bookViews>
   <sheets>
     <sheet name="ibmi_reservations" sheetId="1" r:id="rId1"/>
@@ -1000,23 +1000,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD7C3C09-163B-4F39-AA01-6FCCB64C4C52}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ECA5292-6C72-44A3-A34D-F62A304F74CC}">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="53.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="56" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="56" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.77734375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="58" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="60.109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="40.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">

--- a/ibmi_reservations.xlsx
+++ b/ibmi_reservations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\temp\bob-for-ibmi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7597BCF-8541-47DB-9BCA-A423F007ED2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{98927687-EBA0-4B0E-B887-FFE677BB3720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{916D8ED8-43CB-4AB7-AF7E-14CA3C1C2411}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{997857C9-1777-4110-8BDE-E8E21DDACA3C}"/>
   </bookViews>
   <sheets>
     <sheet name="ibmi_reservations" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="48">
   <si>
     <t>Name</t>
   </si>
@@ -61,18 +61,45 @@
     <t>Shared With</t>
   </si>
   <si>
+    <t>IBM i 7.6 IBM Cloud PowerVS VSI - 2026-08-21 - Created by AskTZ</t>
+  </si>
+  <si>
+    <t>Ready</t>
+  </si>
+  <si>
+    <t>itzpvs-ucc9hi0k</t>
+  </si>
+  <si>
+    <t>161.156.22.60</t>
+  </si>
+  <si>
+    <t>ITZUSER</t>
+  </si>
+  <si>
+    <t>7-vw_gC0OT(FKit</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a8877f865158f1b16546f28</t>
+  </si>
+  <si>
+    <t>2026-08-21 16:10:00Z-2026-08-28 16:10:00 UTC</t>
+  </si>
+  <si>
+    <t>eu-de</t>
+  </si>
+  <si>
+    <t>6a8877f865158f1b16546f28</t>
+  </si>
+  <si>
+    <t>bart_bogaerts@yahoo.com</t>
+  </si>
+  <si>
     <t>IBM i 7.6 IBM Cloud PowerVS VSI - 2026-08-17 - Created by AskTZ</t>
   </si>
   <si>
-    <t>Ready</t>
-  </si>
-  <si>
     <t>itzpvs-mj11hc0k</t>
   </si>
   <si>
-    <t>ITZUSER</t>
-  </si>
-  <si>
     <t>ryK==G13E2O%3o_</t>
   </si>
   <si>
@@ -82,9 +109,6 @@
     <t>2026-08-17 14:51:00Z-2026-08-24 14:51:00 UTC</t>
   </si>
   <si>
-    <t>eu-de</t>
-  </si>
-  <si>
     <t>6a856478b4e22cae9cf3d058</t>
   </si>
   <si>
@@ -121,7 +145,7 @@
     <t>6a831dfe55cacf5a51962fd4</t>
   </si>
   <si>
-    <t>steve.lievens@be.ibm.com</t>
+    <t>bart_bogaerts@be.ibm.com;steve.lievens@be.ibm.com</t>
   </si>
   <si>
     <t>itzpvs-ombq280k</t>
@@ -146,7 +170,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,6 +301,14 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -579,7 +611,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -622,12 +654,14 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -661,6 +695,7 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -1000,8 +1035,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ECA5292-6C72-44A3-A34D-F62A304F74CC}">
-  <dimension ref="A1:M5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B1DE7D1-69CD-438B-BEDD-D2B91D897670}">
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="56" bestFit="1" customWidth="1"/>
@@ -1016,7 +1051,7 @@
     <col min="10" max="10" width="40.5546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6.77734375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="49.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1073,149 +1108,200 @@
       <c r="D2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="1">
-        <v>161156136125</v>
+      <c r="E2" t="s">
+        <v>16</v>
       </c>
       <c r="F2">
         <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s">
         <v>18</v>
       </c>
+      <c r="I2" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E3" s="1">
-        <v>161156136130</v>
+        <v>161156136125</v>
       </c>
       <c r="F3">
         <v>22</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="J3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>28</v>
+        <v>30</v>
+      </c>
+      <c r="E4" s="1">
+        <v>161156136130</v>
       </c>
       <c r="F4">
         <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="J4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F5">
         <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" t="s">
         <v>37</v>
       </c>
+      <c r="I5" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="J5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L5" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="M5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6">
+        <v>22</v>
+      </c>
+      <c r="G6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{3242078F-961D-4826-969B-CFB111537FF8}"/>
+    <hyperlink ref="I3" r:id="rId2" xr:uid="{A0F02FD9-F25C-4B94-9BFC-03A812E6EB64}"/>
+    <hyperlink ref="I4" r:id="rId3" xr:uid="{96EB7326-4EBA-4189-B08D-8F6C47A74586}"/>
+    <hyperlink ref="I5" r:id="rId4" xr:uid="{B0997F1F-A0F7-467A-A6C0-DE0479859196}"/>
+    <hyperlink ref="I6" r:id="rId5" xr:uid="{CE1D9ACB-5B66-4582-8290-6127FAF5D2A4}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>